--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3732,10 +3732,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133907637</v>
+        <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>101305</v>
+        <v>99270</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3743,37 +3743,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222771</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Södra Långviksgruvan, Södra Långviksgruvan, Dlr</t>
+          <t>Holmgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>564813</v>
+        <v>564636</v>
       </c>
       <c r="R30" t="n">
-        <v>6683124</v>
+        <v>6683372</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3797,12 +3801,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3817,27 +3821,31 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133907637</t>
+          <t>https://artportalen.se/Sighting/136932567</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133907204</v>
+        <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>101940</v>
+        <v>99270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,37 +3853,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223366</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svarta vinbär</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ribes nigrum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
+          <t>Holmgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>564896</v>
+        <v>564656</v>
       </c>
       <c r="R31" t="n">
-        <v>6683117</v>
+        <v>6683311</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3899,12 +3911,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3919,27 +3931,31 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133907204</t>
+          <t>https://artportalen.se/Sighting/136932568</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133907687</v>
+        <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>101940</v>
+        <v>99270</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3947,37 +3963,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>223366</v>
+        <v>219790</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svarta vinbär</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ribes nigrum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Södra Långviksgruvan, Södra Långviksgruvan, Dlr</t>
+          <t>Holmgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>564780</v>
+        <v>564697</v>
       </c>
       <c r="R32" t="n">
-        <v>6683077</v>
+        <v>6683229</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4001,12 +4021,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4021,18 +4041,980 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136932571</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136932572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Holmgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>564688</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6683254</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136932572</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136932574</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Holmgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>564687</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6683240</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136932574</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136932569</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99388</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Holmgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>564663</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6683300</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136932569</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136932570</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99388</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Holmgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>564700</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6683221</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136932570</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136932573</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99388</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Holmgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>564690</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6683244</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136932573</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>133907637</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101305</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Södra Långviksgruvan, Södra Långviksgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>564813</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6683124</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
           <t>Patric Engfeldt</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
+      <c r="AX38" t="inlineStr">
         <is>
           <t>Patric Engfeldt</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
-      <c r="AZ32" t="inlineStr">
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133907637</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>133907204</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101940</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>223366</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svarta vinbär</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ribes nigrum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Norra Långviksgruvan, Norra Långviksgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>564896</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6683117</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133907204</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>133907687</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101940</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>223366</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Svarta vinbär</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ribes nigrum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Södra Långviksgruvan, Södra Långviksgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>564780</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6683077</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/133907687</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136932566</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99273</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Holmgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>564630</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6683382</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136932566</t>
         </is>
       </c>
     </row>
@@ -4069,6 +5051,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ41"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5015,6 +5015,452 @@
       <c r="AZ41" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136932566</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136954151</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99273</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Holmgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>564627</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6683389</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954151</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136954149</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99390</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Holmgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>564631</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6683409</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954149</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136954153</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99390</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Holmgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>564627</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6683384</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954153</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136954154</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99390</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Holmgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>564616</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6683408</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954154</t>
         </is>
       </c>
     </row>
@@ -5060,6 +5506,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99398</v>
+        <v>99399</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99398</v>
+        <v>99399</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99398</v>
+        <v>99399</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99399</v>
+        <v>99405</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99399</v>
+        <v>99405</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99399</v>
+        <v>99405</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99405</v>
+        <v>99409</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99405</v>
+        <v>99409</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99405</v>
+        <v>99409</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99407</v>
+        <v>99409</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99407</v>
+        <v>99409</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99407</v>
+        <v>99409</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99411</v>
+        <v>99413</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99411</v>
+        <v>99413</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99411</v>
+        <v>99413</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99413</v>
+        <v>99426</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99413</v>
+        <v>99426</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99413</v>
+        <v>99426</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99426</v>
+        <v>99428</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99426</v>
+        <v>99428</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99426</v>
+        <v>99428</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99426</v>
+        <v>99429</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99426</v>
+        <v>99429</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99426</v>
+        <v>99429</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99428</v>
+        <v>99431</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99428</v>
+        <v>99431</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99428</v>
+        <v>99431</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99429</v>
+        <v>99439</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99429</v>
+        <v>99439</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99429</v>
+        <v>99439</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99431</v>
+        <v>99441</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99431</v>
+        <v>99441</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99431</v>
+        <v>99441</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99439</v>
+        <v>99440</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99439</v>
+        <v>99440</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99439</v>
+        <v>99440</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99441</v>
+        <v>99442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99441</v>
+        <v>99442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99441</v>
+        <v>99442</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99440</v>
+        <v>99445</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99440</v>
+        <v>99445</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99440</v>
+        <v>99445</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99442</v>
+        <v>99447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99442</v>
+        <v>99447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99442</v>
+        <v>99447</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99445</v>
+        <v>99447</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99445</v>
+        <v>99447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99445</v>
+        <v>99447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99447</v>
+        <v>99449</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99447</v>
+        <v>99449</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99447</v>
+        <v>99449</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99447</v>
+        <v>99453</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99447</v>
+        <v>99453</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99447</v>
+        <v>99453</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99449</v>
+        <v>99455</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99449</v>
+        <v>99455</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99449</v>
+        <v>99455</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99453</v>
+        <v>99465</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99453</v>
+        <v>99465</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99453</v>
+        <v>99465</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99455</v>
+        <v>99467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99455</v>
+        <v>99467</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99455</v>
+        <v>99467</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99465</v>
+        <v>99466</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99465</v>
+        <v>99466</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99465</v>
+        <v>99466</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99467</v>
+        <v>99468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99467</v>
+        <v>99468</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99467</v>
+        <v>99468</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99466</v>
+        <v>99469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99466</v>
+        <v>99469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99466</v>
+        <v>99469</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99468</v>
+        <v>99471</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99468</v>
+        <v>99471</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99468</v>
+        <v>99471</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99469</v>
+        <v>99470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99469</v>
+        <v>99470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99469</v>
+        <v>99470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99471</v>
+        <v>99472</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99471</v>
+        <v>99472</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99471</v>
+        <v>99472</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 34929-2024 artfynd.xlsx
+++ b/artfynd/A 34929-2024 artfynd.xlsx
@@ -3735,7 +3735,7 @@
         <v>136932567</v>
       </c>
       <c r="B30" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>136932568</v>
       </c>
       <c r="B31" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136932571</v>
       </c>
       <c r="B32" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136932572</v>
       </c>
       <c r="B33" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136932574</v>
       </c>
       <c r="B34" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>136932569</v>
       </c>
       <c r="B35" t="n">
-        <v>99470</v>
+        <v>99473</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>136932570</v>
       </c>
       <c r="B36" t="n">
-        <v>99470</v>
+        <v>99473</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136932573</v>
       </c>
       <c r="B37" t="n">
-        <v>99470</v>
+        <v>99473</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136932566</v>
       </c>
       <c r="B41" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>136954151</v>
       </c>
       <c r="B42" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>136954149</v>
       </c>
       <c r="B43" t="n">
-        <v>99472</v>
+        <v>99475</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136954153</v>
       </c>
       <c r="B44" t="n">
-        <v>99472</v>
+        <v>99475</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>136954154</v>
       </c>
       <c r="B45" t="n">
-        <v>99472</v>
+        <v>99475</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
